--- a/artfynd/A 36752-2024 artfynd.xlsx
+++ b/artfynd/A 36752-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119684550</v>
+        <v>119685041</v>
       </c>
       <c r="B2" t="n">
         <v>97907</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -718,21 +718,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gods, Gods, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580684</v>
+        <v>580743</v>
       </c>
       <c r="R2" t="n">
-        <v>6698726</v>
+        <v>6698725</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -927,7 +922,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119685041</v>
+        <v>119684550</v>
       </c>
       <c r="B4" t="n">
         <v>97907</v>
@@ -962,7 +957,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -970,16 +965,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gods, Gods, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580743</v>
+        <v>580684</v>
       </c>
       <c r="R4" t="n">
-        <v>6698725</v>
+        <v>6698726</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 36752-2024 artfynd.xlsx
+++ b/artfynd/A 36752-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119685041</v>
+        <v>119685091</v>
       </c>
       <c r="B2" t="n">
         <v>97907</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -718,16 +718,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gods, Gods, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580743</v>
+        <v>580739</v>
       </c>
       <c r="R2" t="n">
-        <v>6698725</v>
+        <v>6698709</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119685091</v>
+        <v>119684550</v>
       </c>
       <c r="B3" t="n">
         <v>97907</v>
@@ -831,7 +836,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -850,10 +855,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580739</v>
+        <v>580684</v>
       </c>
       <c r="R3" t="n">
-        <v>6698709</v>
+        <v>6698726</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,7 +890,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,7 +900,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,7 +927,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119684550</v>
+        <v>119685041</v>
       </c>
       <c r="B4" t="n">
         <v>97907</v>
@@ -957,7 +962,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -965,21 +970,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gods, Gods, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580684</v>
+        <v>580743</v>
       </c>
       <c r="R4" t="n">
-        <v>6698726</v>
+        <v>6698725</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
